--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trolleykw-my.sharepoint.com/personal/m_george_trolley_com_kw/Documents/Documents/GitHub/Trolley-Slimstock-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBC501D1-027A-4CC7-95EE-F4161E38E83B}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{469D93D6-6AF7-49C9-8D9E-35B728E5E66A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t xml:space="preserve">Finished </t>
-  </si>
-  <si>
-    <t>On-Hold</t>
   </si>
 </sst>
 </file>
@@ -588,7 +585,7 @@
         <v>46175</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2">
         <v>7</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trolleykw-my.sharepoint.com/personal/m_george_trolley_com_kw/Documents/Documents/GitHub/Trolley-Slimstock-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{469D93D6-6AF7-49C9-8D9E-35B728E5E66A}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A15FE9-A77D-4E7C-8C30-631EFE14B5CC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,7 +728,7 @@
         <v>46203</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trolleykw-my.sharepoint.com/personal/m_george_trolley_com_kw/Documents/Documents/GitHub/Trolley-Slimstock-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A15FE9-A77D-4E7C-8C30-631EFE14B5CC}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E466996-7E0F-4010-8DF4-733EEBDE5070}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,7 +809,7 @@
         <v>46216</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" s="2">
         <v>10</v>
@@ -821,7 +821,7 @@
         <v>46230</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K12" s="2">
         <v>9</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trolleykw-my.sharepoint.com/personal/m_george_trolley_com_kw/Documents/Documents/GitHub/Trolley-Slimstock-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E466996-7E0F-4010-8DF4-733EEBDE5070}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F5E69D-CF3A-400B-916C-F2812DBA0A6C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
         <v>46205</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trolleykw-my.sharepoint.com/personal/m_george_trolley_com_kw/Documents/Documents/GitHub/Trolley-Slimstock-Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\__Slim 4\Web site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F5E69D-CF3A-400B-916C-F2812DBA0A6C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43BCF54-C278-49FE-BF79-8A8D3EE9CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -821,7 +821,7 @@
         <v>46230</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" s="2">
         <v>9</v>
@@ -844,7 +844,7 @@
         <v>46237</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\__Slim 4\Web site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trolleykw-my.sharepoint.com/personal/m_george_trolley_com_kw/Documents/Documents/GitHub/Trolley-Slimstock-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43BCF54-C278-49FE-BF79-8A8D3EE9CAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{57363359-E1CD-4AD6-9383-D59C6A7C0162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B910AE6B-BFDB-416A-8650-40CBEFB4BE65}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,7 +533,7 @@
         <v>46230</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -585,7 +585,7 @@
         <v>46175</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="2">
         <v>7</v>
@@ -809,7 +809,7 @@
         <v>46216</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="2">
         <v>10</v>
